--- a/импорт/horoshop_chuyka_import.xlsx
+++ b/импорт/horoshop_chuyka_import.xlsx
@@ -800,12 +800,12 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://www.blue-bird.tech/wp-content/uploads/2026/01/avtomobilnij-trimach-dlya-chujka_1-1.jpg</t>
+          <t>BB-24683.jpg</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>https://www.blue-bird.tech/wp-content/uploads/2026/01/avtomobilnij-trimach-dlya-chujka_2.jpg;https://www.blue-bird.tech/wp-content/uploads/2026/01/avtomobilnij-trimach-dlya-chujka_3.jpg;https://www.blue-bird.tech/wp-content/uploads/2026/01/avtomobilnij-trimach-dlya-chujka_8.jpg;https://www.blue-bird.tech/wp-content/uploads/2026/01/avtomobilnij-trimach-dlya-chujka_7.jpg;https://www.blue-bird.tech/wp-content/uploads/2026/01/avtomobilnij-trimach-dlya-chujka_6.jpg;https://www.blue-bird.tech/wp-content/uploads/2026/01/avtomobilnij-trimach-dlya-chujka_5.jpg;https://www.blue-bird.tech/wp-content/uploads/2026/01/avtomobilnij-trimach-dlya-chujka_4.jpg</t>
+          <t>BB-24683@1.jpg;BB-24683@2.jpg;BB-24683@3.jpg;BB-24683@4.jpg;BB-24683@5.jpg;BB-24683@6.jpg;BB-24683@7.jpg</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -821,7 +821,11 @@
           <t>Автомобільний тримач для «Чуйка» — купити, ціна в Україні</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Автомобильный держатель для «Чуйка» — купить, цена в Украине</t>
+        </is>
+      </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
@@ -829,13 +833,21 @@
           <t>Автомобільний тримач для «Чуйка» від Blue Bird Tech. Детектор дронів «Чуйка». Офіційний партнер, гарантія, доставка по Україні.</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Автомобильный держатель для «Чуйка» от Blue Bird Tech. Детектор дронов «Чуйка». Официальный партнёр, гарантия, доставка по Украине.</t>
+        </is>
+      </c>
       <c r="AB2" t="inlineStr">
         <is>
           <t>Автомобільний тримач для «Чуйка»</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Автомобильный держатель для «Чуйка»</t>
+        </is>
+      </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
@@ -896,7 +908,11 @@
           <t>Автомобільний тримач для «Чуйка»</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Автомобильный держатель для «Чуйка»</t>
+        </is>
+      </c>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
@@ -1014,12 +1030,12 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://www.blue-bird.tech/wp-content/uploads/2025/11/1-1.png</t>
+          <t>BB-45041.png</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>https://www.blue-bird.tech/wp-content/uploads/2025/11/vinosna-antena-dlya-dron-detektora-chujka-3-m-kabeli_1.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/11/vinosna-antena-dlya-dron-detektora-chujka-3-m-kabeli_4.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/11/vinosna-antena-dlya-dron-detektora-chujka-3-m-kabeli_2.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/11/vinosna-antena-dlya-dron-detektora-chujka-3-m-kabeli_3.jpg</t>
+          <t>BB-45041@1.jpg;BB-45041@2.jpg;BB-45041@3.jpg;BB-45041@4.jpg</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
@@ -1035,7 +1051,11 @@
           <t>Виносна антена для дрон детектора «Чуйка» 10 м кабель — купити, ціна в Україні</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Выносная антенна для дрон-детектора «Чуйка» (10 м кабеля) — купить, цена в Украине</t>
+        </is>
+      </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
@@ -1043,13 +1063,21 @@
           <t>Виносна антена для дрон детектора «Чуйка» 10 м кабель від Blue Bird Tech. Детектор дронів «Чуйка». Офіційний партнер, гарантія, доставка по Україні.</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Выносная антенна для дрон-детектора «Чуйка» (10 м кабеля) от Blue Bird Tech. Детектор дронов «Чуйка». Официальный партнёр, гарантия, доставка по Украине.</t>
+        </is>
+      </c>
       <c r="AB3" t="inlineStr">
         <is>
           <t>Виносна антена для дрон детектора «Чуйка» 10 м кабель</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Выносная антенна для дрон-детектора «Чуйка» (10 м кабеля)</t>
+        </is>
+      </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
@@ -1101,7 +1129,11 @@
           <t>Виносна антена для дрон детектора «Чуйка» 10 м кабель</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Выносная антенна для дрон-детектора «Чуйка» (10 м кабеля)</t>
+        </is>
+      </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
@@ -1219,12 +1251,12 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://www.blue-bird.tech/wp-content/uploads/2025/11/1-1.png</t>
+          <t>BB-16387.png</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>https://www.blue-bird.tech/wp-content/uploads/2025/11/vinosna-antena-dlya-dron-detektora-chujka-3-m-kabeli_1.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/11/vinosna-antena-dlya-dron-detektora-chujka-3-m-kabeli_4.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/11/vinosna-antena-dlya-dron-detektora-chujka-3-m-kabeli_2.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/11/vinosna-antena-dlya-dron-detektora-chujka-3-m-kabeli_3.jpg</t>
+          <t>BB-16387@1.jpg;BB-16387@2.jpg;BB-16387@3.jpg;BB-16387@4.jpg</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
@@ -1240,7 +1272,11 @@
           <t>Виносна антена для дрон детектора «Чуйка» 3 м кабель — купити, ціна в Україні</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Выносная антенна для дрон-детектора «Чуйка» (3 м кабеля) — купить, цена в Украине</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
@@ -1248,13 +1284,21 @@
           <t>Виносна антена для дрон детектора «Чуйка» 3 м кабель від Blue Bird Tech. Детектор дронів «Чуйка». Офіційний партнер, гарантія, доставка по Україні.</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Выносная антенна для дрон-детектора «Чуйка» (3 м кабеля) от Blue Bird Tech. Детектор дронов «Чуйка». Официальный партнёр, гарантия, доставка по Украине.</t>
+        </is>
+      </c>
       <c r="AB4" t="inlineStr">
         <is>
           <t>Виносна антена для дрон детектора «Чуйка» 3 м кабель</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Выносная антенна для дрон-детектора «Чуйка» (3 м кабеля)</t>
+        </is>
+      </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
@@ -1306,7 +1350,11 @@
           <t>Виносна антена для дрон детектора «Чуйка» 3 м кабель</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Выносная антенна для дрон-детектора «Чуйка» (3 м кабеля)</t>
+        </is>
+      </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
@@ -1424,12 +1472,12 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://www.blue-bird.tech/wp-content/uploads/2025/11/1-1.png</t>
+          <t>BB-45039.png</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>https://www.blue-bird.tech/wp-content/uploads/2025/11/vinosna-antena-dlya-dron-detektora-chujka-3-m-kabeli_1.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/11/vinosna-antena-dlya-dron-detektora-chujka-3-m-kabeli_4.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/11/vinosna-antena-dlya-dron-detektora-chujka-3-m-kabeli_2.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/11/vinosna-antena-dlya-dron-detektora-chujka-3-m-kabeli_3.jpg</t>
+          <t>BB-45039@1.jpg;BB-45039@2.jpg;BB-45039@3.jpg;BB-45039@4.jpg</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
@@ -1445,7 +1493,11 @@
           <t>Виносна антена для дрон детектора «Чуйка» 5 м кабель — купити, ціна в Україні</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Выносная антенна для дрон-детектора «Чуйка» (5 м кабеля) — купить, цена в Украине</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
@@ -1453,13 +1505,21 @@
           <t>Виносна антена для дрон детектора «Чуйка» 5 м кабель від Blue Bird Tech. Детектор дронів «Чуйка». Офіційний партнер, гарантія, доставка по Україні.</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Выносная антенна для дрон-детектора «Чуйка» (5 м кабеля) от Blue Bird Tech. Детектор дронов «Чуйка». Официальный партнёр, гарантия, доставка по Украине.</t>
+        </is>
+      </c>
       <c r="AB5" t="inlineStr">
         <is>
           <t>Виносна антена для дрон детектора «Чуйка» 5 м кабель</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Выносная антенна для дрон-детектора «Чуйка» (5 м кабеля)</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
@@ -1511,7 +1571,11 @@
           <t>Виносна антена для дрон детектора «Чуйка» 5 м кабель</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Выносная антенна для дрон-детектора «Чуйка» (5 м кабеля)</t>
+        </is>
+      </c>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
@@ -1589,7 +1653,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Кріплення для фіксації «Чуйка 3 0»</t>
+          <t>Кріплення для детектора дронів «Чуйка»</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1629,42 +1693,54 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://www.blue-bird.tech/wp-content/uploads/2025/11/dsc07141-scaled.jpg</t>
+          <t>BB-19441.jpg</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>https://www.blue-bird.tech/wp-content/uploads/2025/11/dsc07142-scaled.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/11/dsc07143-scaled.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/11/dsc07153-scaled.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/11/dsc07154-scaled.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/11/dsc07155-scaled.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/11/dsc07148-scaled.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/11/dsc07149-scaled.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/11/dsc07150-scaled.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/11/dsc07151-scaled.jpg</t>
+          <t>BB-19441@1.jpg;BB-19441@2.jpg;BB-19441@3.jpg;BB-19441@4.jpg;BB-19441@5.jpg;BB-19441@6.jpg;BB-19441@7.jpg;BB-19441@8.jpg;BB-19441@9.jpg</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>kriplennia-dlia-fiksatsii-chuika-3-0</t>
+          <t>kriplennia-dlia-detektora-droniv-chuika</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Кріплення для фіксації «Чуйка 3 0» — купити, ціна в Україні</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr"/>
+          <t>Кріплення для детектора дронів «Чуйка» — купити, ціна в Україні</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Крепление для детектора дронов «Чуйка» — купить, цена в Украине</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Кріплення для фіксації «Чуйка 3 0» від Blue Bird Tech. Детектор дронів «Чуйка». Офіційний партнер, гарантія, доставка по Україні.</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr"/>
+          <t>Кріплення для детектора дронів «Чуйка» від Blue Bird Tech. Детектор дронів «Чуйка». Офіційний партнер, гарантія, доставка по Україні.</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Крепление для детектора дронов «Чуйка» от Blue Bird Tech. Детектор дронов «Чуйка». Официальный партнёр, гарантия, доставка по Украине.</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Кріплення для фіксації «Чуйка 3 0»</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+          <t>Кріплення для детектора дронів «Чуйка»</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Крепление для детектора дронов «Чуйка»</t>
+        </is>
+      </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1702,10 +1778,14 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Кріплення для фіксації «Чуйка 3 0»</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr"/>
+          <t>Кріплення для детектора дронів «Чуйка»</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Крепление для детектора дронов «Чуйка»</t>
+        </is>
+      </c>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
@@ -1728,7 +1808,7 @@
       <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Кріплення для фіксації «Чуйка 3 0»</t>
+          <t>Кріплення для детектора дронів «Чуйка»</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr"/>
@@ -1823,12 +1903,12 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://www.blue-bird.tech/wp-content/uploads/2025/02/image_2026-03-23_12-35-36.png</t>
+          <t>BB-9333.png</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>https://www.blue-bird.tech/wp-content/uploads/2025/02/chujka-blakitna.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/02/chujka-fuksiya.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/02/chujka-oliva.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/02/chujka-fiolet.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/02/chujka-zhovta.jpg;https://www.blue-bird.tech/wp-content/uploads/2025/02/chujka-chervona.jpg</t>
+          <t>BB-9333@1.jpg;BB-9333@2.jpg;BB-9333@3.jpg;BB-9333@4.jpg;BB-9333@5.jpg;BB-9333@6.jpg</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1844,7 +1924,11 @@
           <t>Пристрій радіоелектронної розвідки «Чуйка 3.0» — купити, ціна в Україні</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Устройство радиоэлектронной разведки «Чуйка 3.0» — купить, цена в Украине</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
@@ -1852,13 +1936,21 @@
           <t>Пристрій радіоелектронної розвідки «Чуйка 3.0» від Blue Bird Tech. Детектор дронів «Чуйка». Офіційний партнер, гарантія, доставка по Україні.</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Устройство радиоэлектронной разведки «Чуйка 3.0» от Blue Bird Tech. Детектор дронов «Чуйка». Официальный партнёр, гарантия, доставка по Украине.</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr">
         <is>
           <t>Пристрій радіоелектронної розвідки «Чуйка 3.0»</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Устройство радиоэлектронной разведки «Чуйка 3.0»</t>
+        </is>
+      </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1884,7 +1976,7 @@
 &lt;/ol&gt;
 &lt;p&gt;Завдяки пасивному режиму роботи «Чуйка 3.0» залишається повністю непомітною для противника, водночас забезпечуючи ефективне виявлення БПЛА на відстані до 4 км (залежно від умов і антен).&lt;/p&gt;
 &lt;h3&gt;Нова опція для «Чуйка 3.0»: більше комфорту та безпеки&lt;/h3&gt;
-&lt;p&gt;&lt;img fetchpriority="high" decoding="async" class="aligncenter wp-image-47043 size-large" src="https://www.blue-bird.tech/wp-content/uploads/2026/06/videoout3-1024x608.jpg" alt="" width="640" height="380" srcset="https://www.blue-bird.tech/wp-content/uploads/2026/06/videoout3-1024x608.jpg 1024w, https://www.blue-bird.tech/wp-content/uploads/2026/06/videoout3-300x178.jpg 300w, https://www.blue-bird.tech/wp-content/uploads/2026/06/videoout3-768x456.jpg 768w, https://www.blue-bird.tech/wp-content/uploads/2026/06/videoout3.jpg 1252w" sizes="(max-width: 640px) 100vw, 640px" /&gt;&lt;/p&gt;
+&lt;p&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Відеовихід&lt;/strong&gt;: Підключайте зовнішній екран для безпечного моніторингу з укриття.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Характеристики:&lt;/strong&gt;&lt;/p&gt;&lt;table&gt;&lt;tr&gt;&lt;td&gt;Тип&lt;/td&gt;&lt;td&gt;Пристрій радіоелектронної розвідки&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Частотні діапазони&lt;/td&gt;&lt;td&gt;1.2 ГГц / 3.3 ГГц / 5.8 ГГц&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Діапазони частот сканування:&lt;/td&gt;&lt;td&gt;900-1800 МГц 2870-4080 МГц 4860-6060 МГц&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Тип сигналу&lt;/td&gt;&lt;td&gt;Аналоговий&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Швидкість сканування&lt;/td&gt;&lt;td&gt;4-8 секунди (весь діапазон частот)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Живлення&lt;/td&gt;&lt;td&gt;8.4V (2S)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Ємність акумуляторів&lt;/td&gt;&lt;td&gt;4500 mAh (6 годин роботи)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Габаритні розміри&lt;/td&gt;&lt;td&gt;95 х 158 х 47 мм (без антен та додаткового обладнання)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Вага&lt;/td&gt;&lt;td&gt;до 650 гр&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Малий екран&lt;/td&gt;&lt;td&gt;для виведення службової інформації&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Великий екран&lt;/td&gt;&lt;td&gt;для відображення перехопленого відеосигналу&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Охолодження&lt;/td&gt;&lt;td&gt;Активне, вентилятор із фільтром&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Робоча температура&lt;/td&gt;&lt;td&gt;від –10°C до +50°C&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Матеріал корпусу&lt;/td&gt;&lt;td&gt;PETG&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Захист корпусу&lt;/td&gt;&lt;td&gt;IP54&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;Комплектація&lt;/td&gt;&lt;td&gt;Пристрій.
 3 антени.
 Посібник користувача.
@@ -1909,7 +2001,7 @@
 &lt;/ol&gt;
 &lt;p&gt;Благодаря пассивному режиму работы «Чуйка 3.0» остается полностью незаметной для противника, одновременно обеспечивая эффективное обнаружение БПЛА на расстоянии до 4 км (в зависимости от условий и антенн).&lt;/p&gt;
 &lt;h3&gt;Новая опция для «Чуйка 3.0»: больше комфорта и безопасности&lt;/h3&gt;
-&lt;p&gt;&lt;img fetchpriority="high" decoding="async" class="aligncenter wp-image-47043 size-large" src="https://www.blue-bird.tech/wp-content/uploads/2026/06/videoout3-1024x608.jpg" alt="" width="640" height="380" srcset="https://www.blue-bird.tech/wp-content/uploads/2026/06/videoout3-1024x608.jpg 1024w, https://www.blue-bird.tech/wp-content/uploads/2026/06/videoout3-300x178.jpg 300w, https://www.blue-bird.tech/wp-content/uploads/2026/06/videoout3-768x456.jpg 768w, https://www.blue-bird.tech/wp-content/uploads/2026/06/videoout3.jpg 1252w" sizes="(max-width: 640px) 100vw, 640px" /&gt;&lt;/p&gt;
+&lt;p&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Видеовыход&lt;/strong&gt;: Подключайте внешний экран для безопасного мониторинга по укрытию.&lt;/p&gt;</t>
         </is>
       </c>
@@ -1918,7 +2010,11 @@
           <t>Пристрій радіоелектронної розвідки «Чуйка 3.0»</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Устройство радиоэлектронной разведки «Чуйка 3.0»</t>
+        </is>
+      </c>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
@@ -2036,12 +2132,12 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://www.blue-bird.tech/wp-content/uploads/2026/06/1-1.jpg</t>
+          <t>BB-46856.jpg</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>https://www.blue-bird.tech/wp-content/uploads/2026/06/2-1.jpg;https://www.blue-bird.tech/wp-content/uploads/2026/06/4-1.jpg;https://www.blue-bird.tech/wp-content/uploads/2026/06/5-1.jpg;https://www.blue-bird.tech/wp-content/uploads/2026/06/2.1.jpg;https://www.blue-bird.tech/wp-content/uploads/2026/06/dsc_7103_compressed.jpeg</t>
+          <t>BB-46856@1.jpg;BB-46856@2.jpg;BB-46856@3.jpg;BB-46856@4.jpg;BB-46856@5.jpg</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
@@ -2057,7 +2153,11 @@
           <t>Пристрій радіоелектронної розвідки «Чуйка 4.0» — купити, ціна в Україні</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Устройство радиоэлектронной разведки «Чуйка 4.0» — купить, цена в Украине</t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr">
@@ -2065,13 +2165,21 @@
           <t>Пристрій радіоелектронної розвідки «Чуйка 4.0» від Blue Bird Tech. Детектор дронів «Чуйка». Офіційний партнер, гарантія, доставка по Україні.</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Устройство радиоэлектронной разведки «Чуйка 4.0» от Blue Bird Tech. Детектор дронов «Чуйка». Официальный партнёр, гарантия, доставка по Украине.</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr">
         <is>
           <t>Пристрій радіоелектронної розвідки «Чуйка 4.0»</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Устройство радиоэлектронной разведки «Чуйка 4.0»</t>
+        </is>
+      </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
@@ -2137,7 +2245,11 @@
           <t>Пристрій радіоелектронної розвідки «Чуйка 4.0»</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Устройство радиоэлектронной разведки «Чуйка 4.0»</t>
+        </is>
+      </c>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
